--- a/dados/TABELAS_NE.xlsx
+++ b/dados/TABELAS_NE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Fábio\Desktop\CRM_APP\dados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C55165E-A05F-4687-9E63-C7F2EC85BCE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4133AF57-EC88-4290-AF8F-3644A0996776}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{F9AC85B4-4295-4675-8D5B-618F5EEE6B49}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="943" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="943" uniqueCount="119">
   <si>
     <t>CÓD.</t>
   </si>
@@ -377,6 +377,12 @@
   </si>
   <si>
     <t>25gr</t>
+  </si>
+  <si>
+    <t>PRECO</t>
+  </si>
+  <si>
+    <t>ID_COD</t>
   </si>
 </sst>
 </file>
@@ -691,7 +697,7 @@
     <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -923,10 +929,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1265,7 +1268,7 @@
   <sheetData>
     <row r="1" spans="1:10" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="79" t="s">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="B1" s="79" t="s">
         <v>1</v>
@@ -1285,39 +1288,39 @@
       <c r="G1" s="79" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="80" t="s">
+      <c r="H1" s="79" t="s">
         <v>93</v>
       </c>
       <c r="I1" s="79" t="s">
-        <v>5</v>
+        <v>117</v>
       </c>
       <c r="J1" s="26">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="46">
+      <c r="A2" s="75">
         <v>8</v>
       </c>
-      <c r="B2" s="51" t="s">
+      <c r="B2" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="51" t="s">
+      <c r="C2" s="53" t="s">
         <v>98</v>
       </c>
-      <c r="D2" s="51" t="s">
+      <c r="D2" s="53" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="51">
+      <c r="E2" s="53">
         <v>72</v>
       </c>
-      <c r="F2" s="56" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" s="56" t="s">
-        <v>10</v>
-      </c>
-      <c r="H2" s="46" t="s">
+      <c r="F2" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="75" t="s">
         <v>11</v>
       </c>
       <c r="I2" s="30">
@@ -6076,7 +6079,7 @@
         <v>25</v>
       </c>
       <c r="I66" s="32">
-        <f t="shared" ref="I66:I97" si="2">(J66*$J$1)+J66</f>
+        <f t="shared" ref="I66:I68" si="2">(J66*$J$1)+J66</f>
         <v>9.6199999999999992</v>
       </c>
       <c r="J66" s="32">
